--- a/reports/analytics/q10_product_categories_comparison.xlsx
+++ b/reports/analytics/q10_product_categories_comparison.xlsx
@@ -439,7 +439,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>LOGEMENT, EAU, GAZ, ELECTRICITE ET AUTRES COMBUSTIBLES</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -478,7 +478,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>RESTAURANTS ET HOTELS</t>
+          <t>SANTE</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -491,7 +491,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ENSEIGNEMENT</t>
+          <t>RESTAURANTS ET HOTELS</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -504,7 +504,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PRODUITS ALIMENTAIRES</t>
+          <t>LOGEMENT, EAU, GAZ, ELECTRICITE ET AUTRES COMBUSTIBLES</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -530,7 +530,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>COMMUNICATIONS</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -543,7 +543,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PRODUITS ALIMENTAIRES ET BOISSONS NON ALCOOLISEES</t>
+          <t>MEUBLES, ARTICLES DE MENAGE ET ENTRETIEN COURANT DU FOYER</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BOISSONS ALCOOLISEES, TABAC ET STUPEFIANTS</t>
+          <t>PRODUITS ALIMENTAIRES</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -582,7 +582,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SANTE</t>
+          <t>BOISSONS ALCOOLISEES, TABAC ET STUPEFIANTS</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -595,7 +595,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>COMMUNICATIONS</t>
+          <t>PRODUITS ALIMENTAIRES ET BOISSONS NON ALCOOLISEES</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -621,7 +621,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MEUBLES, ARTICLES DE MENAGE ET ENTRETIEN COURANT DU FOYER</t>
+          <t>ENSEIGNEMENT</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -790,7 +790,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SANTE</t>
+          <t>RESTAURANTS ET HOTELS</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -803,7 +803,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>RESTAURANTS ET HOTELS</t>
+          <t>SANTE</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -998,7 +998,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SANTE</t>
+          <t>ARTICLES D'HABILLEMENT ET CHAUSSURES</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ARTICLES D'HABILLEMENT ET CHAUSSURES</t>
+          <t>SANTE</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>RESTAURANTS ET HOTELS</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>RESTAURANTS ET HOTELS</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>PRODUITS ALIMENTAIRES</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>PRODUITS ALIMENTAIRES</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>COMMUNICATIONS</t>
+          <t>MEUBLES, ARTICLES DE MENAGE ET ENTRETIEN COURANT DU FOYER</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>MEUBLES, ARTICLES DE MENAGE ET ENTRETIEN COURANT DU FOYER</t>
+          <t>COMMUNICATIONS</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>ARTICLES D'HABILLEMENT ET CHAUSSURES</t>
+          <t>MEUBLES, ARTICLES DE MENAGE ET ENTRETIEN COURANT DU FOYER</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
@@ -2205,7 +2205,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>PRODUITS ALIMENTAIRES ET BOISSONS NON ALCOOLISEES</t>
+          <t>PRODUITS ALIMENTAIRES</t>
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>PRODUITS NON ALIMENTAIRES</t>
+          <t>ENSEIGNEMENT</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
@@ -2227,7 +2227,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>ENSEIGNEMENT</t>
+          <t>RESTAURANTS ET HOTELS</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
@@ -2249,7 +2249,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>LOGEMENT, EAU, GAZ, ELECTRICITE ET AUTRES COMBUSTIBLES</t>
+          <t>PRODUITS ALIMENTAIRES ET BOISSONS NON ALCOOLISEES</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>BIENS ET SERVICES DIVERS</t>
+          <t>ARTICLES D'HABILLEMENT ET CHAUSSURES</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>RESTAURANTS ET HOTELS</t>
+          <t>LOGEMENT, EAU, GAZ, ELECTRICITE ET AUTRES COMBUSTIBLES</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>SANTE</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
@@ -2293,7 +2293,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>TRANSPORTS</t>
+          <t>PRODUITS NON ALIMENTAIRES</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>SANTE</t>
+          <t>BIENS ET SERVICES DIVERS</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
@@ -2326,7 +2326,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>COMMUNICATIONS</t>
+          <t>GENERAL</t>
         </is>
       </c>
       <c r="C149" t="inlineStr"/>
@@ -2337,7 +2337,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>PRODUITS ALIMENTAIRES</t>
+          <t>TRANSPORTS</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>MEUBLES, ARTICLES DE MENAGE ET ENTRETIEN COURANT DU FOYER</t>
+          <t>COMMUNICATIONS</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
